--- a/TestSelenium/src/test/resources/test-data.xlsx
+++ b/TestSelenium/src/test/resources/test-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Year 4\Software Testing and Quality Assurance\Assignment_2\TestSelenium\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6A712C-0529-4A9A-8D81-A7D99F96FED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FD6137-0D6C-42F3-87AE-94DCA07ABB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{763D8013-566B-4590-9641-73BF4B3B78CF}"/>
   </bookViews>
@@ -105,10 +105,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -131,13 +139,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -512,7 +523,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
@@ -547,7 +558,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{336FBAD5-1DD1-44A7-8EC5-166D2880BE11}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
--- a/TestSelenium/src/test/resources/test-data.xlsx
+++ b/TestSelenium/src/test/resources/test-data.xlsx
@@ -8,12 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Year 4\Software Testing and Quality Assurance\Assignment_2\TestSelenium\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FD6137-0D6C-42F3-87AE-94DCA07ABB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7ACD11-763C-48EC-845E-260012C0EE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{763D8013-566B-4590-9641-73BF4B3B78CF}"/>
+    <workbookView xWindow="1127" yWindow="1127" windowWidth="18031" windowHeight="9304" activeTab="1" xr2:uid="{763D8013-566B-4590-9641-73BF4B3B78CF}"/>
   </bookViews>
   <sheets>
     <sheet name="CheckoutProcess" sheetId="1" r:id="rId1"/>
+    <sheet name="ValidLogin" sheetId="2" r:id="rId2"/>
+    <sheet name="InvalidLogin" sheetId="3" r:id="rId3"/>
+    <sheet name="ValidRegistration" sheetId="4" r:id="rId4"/>
+    <sheet name="RegistrationValidationErrors" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="39">
   <si>
     <t>alice05@example.com</t>
   </si>
@@ -99,6 +104,63 @@
   </si>
   <si>
     <t>comment</t>
+  </si>
+  <si>
+    <t>expectedTitle</t>
+  </si>
+  <si>
+    <t>expectedLogoutVisible</t>
+  </si>
+  <si>
+    <t>My Account</t>
+  </si>
+  <si>
+    <t>expectedErrorMessage</t>
+  </si>
+  <si>
+    <t>wrongpassword</t>
+  </si>
+  <si>
+    <t>Warning: No match for E-Mail Address and/or Password.</t>
+  </si>
+  <si>
+    <t>Account Login</t>
+  </si>
+  <si>
+    <t>telephone</t>
+  </si>
+  <si>
+    <t>confirmPassword</t>
+  </si>
+  <si>
+    <t>expectedSuccessMessage</t>
+  </si>
+  <si>
+    <t>Your Account Has Been Created!</t>
+  </si>
+  <si>
+    <t>expectedEmailError</t>
+  </si>
+  <si>
+    <t>expectedTelephoneError</t>
+  </si>
+  <si>
+    <t>expectedPasswordError</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>E-Mail Address does not appear to be valid!</t>
+  </si>
+  <si>
+    <t>Telephone must be between 3 and 32 characters!</t>
+  </si>
+  <si>
+    <t>Password must be between 4 and 20 characters!</t>
+  </si>
+  <si>
+    <t>valid@example.com</t>
   </si>
 </sst>
 </file>
@@ -564,4 +626,224 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139FB9E0-6030-4276-AB03-32C7C3F57A3E}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF61071-164B-4D5E-8FB9-E817E0AA8500}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68F3E6B5-4091-4ACD-A23A-514BA22AC00F}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>1234567890</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173CFE6C-6D3F-42F9-A049-18F4FF8389F3}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3">
+        <v>1234567890</v>
+      </c>
+      <c r="E3">
+        <v>123</v>
+      </c>
+      <c r="F3">
+        <v>123</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2F7B43-8B32-47F2-8F1B-0BB4E7B015FD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/TestSelenium/src/test/resources/test-data.xlsx
+++ b/TestSelenium/src/test/resources/test-data.xlsx
@@ -2,23 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Year 4\Software Testing and Quality Assurance\Assignment_2\TestSelenium\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO I3\Documents\year4\term2\testing\final vision of it p2\SoftwareTestingA2\TestSelenium\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7ACD11-763C-48EC-845E-260012C0EE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85644C23-6CA6-4041-AB66-5523490F82CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1127" yWindow="1127" windowWidth="18031" windowHeight="9304" activeTab="1" xr2:uid="{763D8013-566B-4590-9641-73BF4B3B78CF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{763D8013-566B-4590-9641-73BF4B3B78CF}"/>
   </bookViews>
   <sheets>
     <sheet name="CheckoutProcess" sheetId="1" r:id="rId1"/>
     <sheet name="ValidLogin" sheetId="2" r:id="rId2"/>
-    <sheet name="InvalidLogin" sheetId="3" r:id="rId3"/>
-    <sheet name="ValidRegistration" sheetId="4" r:id="rId4"/>
-    <sheet name="RegistrationValidationErrors" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
+    <sheet name="CurrencyData" sheetId="7" r:id="rId3"/>
+    <sheet name="SearchData" sheetId="8" r:id="rId4"/>
+    <sheet name="ShoppingCartData" sheetId="9" r:id="rId5"/>
+    <sheet name="InvalidLogin" sheetId="3" r:id="rId6"/>
+    <sheet name="ValidRegistration" sheetId="4" r:id="rId7"/>
+    <sheet name="RegistrationValidationErrors" sheetId="5" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,8 +35,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
   <si>
     <t>alice05@example.com</t>
   </si>
@@ -161,13 +162,73 @@
   </si>
   <si>
     <t>valid@example.com</t>
+  </si>
+  <si>
+    <t>testName</t>
+  </si>
+  <si>
+    <t>initialCurrency</t>
+  </si>
+  <si>
+    <t>changedCurrency</t>
+  </si>
+  <si>
+    <t>Default dollar then switch to euro</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>€</t>
+  </si>
+  <si>
+    <t>Default euro then switch to pound</t>
+  </si>
+  <si>
+    <t>£</t>
+  </si>
+  <si>
+    <t>Default pound then switch to dollar</t>
+  </si>
+  <si>
+    <t>keyword</t>
+  </si>
+  <si>
+    <t>Search Mac product</t>
+  </si>
+  <si>
+    <t>Mac</t>
+  </si>
+  <si>
+    <t>tabletName</t>
+  </si>
+  <si>
+    <t>laptopName</t>
+  </si>
+  <si>
+    <t>deliveryDate</t>
+  </si>
+  <si>
+    <t>expectedTabletPrice</t>
+  </si>
+  <si>
+    <t>Add multiple items to cart</t>
+  </si>
+  <si>
+    <t>user22222@gmail.com</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy Tab 10.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +240,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -205,9 +274,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -544,7 +628,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A68B5E-5719-4042-87C0-3DAC64ED1D45}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -631,7 +715,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139FB9E0-6030-4276-AB03-32C7C3F57A3E}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -667,9 +751,152 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37EFEC6C-BB50-4E0A-833B-BEF28B04E9D5}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBEFFE61-D2E7-4B73-96AE-4EBC067EDD99}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF032B44-68DE-4A5F-9056-E735159BFDB7}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="3">
+        <v>12345</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="5">
+        <v>46157</v>
+      </c>
+      <c r="G2" s="6">
+        <v>199.99</v>
+      </c>
+      <c r="H2" s="6"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="mailto:user22222@gmail.com" xr:uid="{D4A6A227-BF23-45DA-A30C-2DCAAE148808}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF61071-164B-4D5E-8FB9-E817E0AA8500}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -704,10 +931,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68F3E6B5-4091-4ACD-A23A-514BA22AC00F}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
@@ -757,10 +984,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{173CFE6C-6D3F-42F9-A049-18F4FF8389F3}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -839,10 +1066,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2F7B43-8B32-47F2-8F1B-0BB4E7B015FD}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
